--- a/outputs/Tabla1_SPR_Anual_LBSPR.xlsx
+++ b/outputs/Tabla1_SPR_Anual_LBSPR.xlsx
@@ -32,10 +32,10 @@
     <t xml:space="preserve">SPR_obs</t>
   </si>
   <si>
-    <t xml:space="preserve">SPR_MLS24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPR_MLS25</t>
+    <t xml:space="preserve">SPR_MCRS24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPR_MCRS25</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA_SPR_pp</t>
